--- a/PlantillaMVC/Export/Temp3.xlsx
+++ b/PlantillaMVC/Export/Temp3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <x:si>
     <x:t>Numero Empleado SAP</x:t>
   </x:si>
@@ -40,55 +40,13 @@
     <x:t>Métrica</x:t>
   </x:si>
   <x:si>
-    <x:t>Peso del objetivo(%)</x:t>
-  </x:si>
-  <x:si>
     <x:t>Resultado</x:t>
   </x:si>
   <x:si>
     <x:t>Comentarios jefe</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Vacante Vac </x:t>
-  </x:si>
-  <x:si>
-    <x:t>Vacante</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Felipe Vargas Vargas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sin objetivos en el periodo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hector Rodrigo Vargas Vargas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tester</x:t>
-  </x:si>
-  <x:si>
-    <x:t>a</x:t>
-  </x:si>
-  <x:si>
-    <x:t>solo el 92%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>queda a un 95%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>b</x:t>
-  </x:si>
-  <x:si>
-    <x:t>se cumple al 100%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>c</x:t>
-  </x:si>
-  <x:si>
-    <x:t>completado al 100%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>queda a un 90%</x:t>
+    <x:t>Peso ponderado %</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -115,7 +73,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -126,12 +84,6 @@
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFF0F8FF"/>
         <x:bgColor rgb="FFF0F8FF"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFFFE0"/>
-        <x:bgColor rgb="FFFFFFE0"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -154,7 +106,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="8">
+  <x:cellStyleXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -164,23 +116,11 @@
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="8">
+  <x:cellXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -191,22 +131,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
@@ -508,14 +432,14 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K5"/>
+  <x:dimension ref="A1:K1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="15.710625" style="0" customWidth="1"/>
     <x:col min="2" max="4" width="35.710625" style="0" customWidth="1"/>
     <x:col min="5" max="6" width="40.710625" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="40.710625" style="7" customWidth="1"/>
-    <x:col min="8" max="8" width="45.710625" style="7" customWidth="1"/>
+    <x:col min="7" max="7" width="40.710625" style="3" customWidth="1"/>
+    <x:col min="8" max="8" width="45.710625" style="3" customWidth="1"/>
     <x:col min="9" max="11" width="45.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -552,136 +476,6 @@
       </x:c>
       <x:c r="K1" s="1" t="s">
         <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:11" s="3" customFormat="1">
-      <x:c r="A2" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B2" s="3" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C2" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="3" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E2" s="3" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F2" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G2" s="4" t="s"/>
-      <x:c r="H2" s="4" t="s"/>
-      <x:c r="I2" s="3" t="s"/>
-      <x:c r="J2" s="3" t="s"/>
-      <x:c r="K2" s="3" t="s"/>
-    </x:row>
-    <x:row r="3" spans="1:11" s="5" customFormat="1">
-      <x:c r="A3" s="5" t="n">
-        <x:v>15072017</x:v>
-      </x:c>
-      <x:c r="B3" s="5" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C3" s="5" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="5" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E3" s="5" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F3" s="5" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G3" s="6" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H3" s="6" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I3" s="5" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="J3" s="5" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="K3" s="5" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:11" s="5" customFormat="1">
-      <x:c r="A4" s="5" t="n">
-        <x:v>15072017</x:v>
-      </x:c>
-      <x:c r="B4" s="5" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C4" s="5" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="5" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E4" s="5" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F4" s="5" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="G4" s="6" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H4" s="6" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="I4" s="5" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="J4" s="5" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="K4" s="5" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:11">
-      <x:c r="A5" s="0" t="n">
-        <x:v>15072017</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G5" s="7" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H5" s="7" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="I5" s="0" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="K5" s="0" t="s">
-        <x:v>24</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/PlantillaMVC/Export/Temp3.xlsx
+++ b/PlantillaMVC/Export/Temp3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="120">
   <x:si>
     <x:t>Numero Empleado SAP</x:t>
   </x:si>
@@ -40,13 +40,537 @@
     <x:t>Métrica</x:t>
   </x:si>
   <x:si>
+    <x:t>Peso del objetivo(%)</x:t>
+  </x:si>
+  <x:si>
     <x:t>Resultado</x:t>
   </x:si>
   <x:si>
     <x:t>Comentarios jefe</x:t>
   </x:si>
   <x:si>
-    <x:t>Peso ponderado %</x:t>
+    <x:t xml:space="preserve">Gabriel Alejandro Spinazzola  </x:t>
+  </x:si>
+  <x:si>
+    <x:t>Finanzas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gerente de Finanzas Cono Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Christian Leonardo  Quiroga </x:t>
+  </x:si>
+  <x:si>
+    <x:t>To achieve FY 2026 EBITDA as budgeted  (Euro 22,4MM)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. GTN
+2. % of deviation
+3. Delta ppt
+4. % achievement
+5. GP over % bottom
+6. % deviation
+7. % deviation
+8. 300k EUR
+9. 100 k EUR
+10. between 54 and 80 days
+11. 5% less than prior month
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t>To improve Working capital</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Track Argentina DSO under 90 days and Chile DSO under 110 days in a monthly base trough weekly finance report
+2. Deep follow up Chile accounts during each months based on 5 top key accounts from new Argentina admin structure not exceding 120 days 
+3. Elevate after each month close to commercial any find to avoid customer to fall in due dates stopping deliveries if not pay
+4. Monthly follow up of % succes factor of plant deliveries to adjust DIO each sku/brand under 198 days in average
+5. Monthly follow up of FA vs budget units achieving at least 70% in each X brand 
+6. Monitor and adjust every month into IBP process PO to differents plants maximizing inventories avoiding order cancelation to cero trough APA highlights
+7. Detect 80/20 sku deviation identifying source and set action plan (+ inventory vs dicontinuation) during PMR process and follow up action plan to reduce inventory balance to reduce 50% gap in next 12 months 
+8. Monthly follow up of FA vs budget units achieving at least 70% in each X brand 
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. DSO
+2. top 5 clients
+3. &gt;120 days not collection
+4. DIO
+5. X Brand FA 
+6. Cero order cancellation
+7. % gap reduction
+8. X Brand FA 
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Achieve Demand Plan Accuracy</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Monthly follow up of FA vs budget units achieving at least 70% in each X brand 
+2. Detect 80/20 sku deviation identifying source plant and set action plan (+ inventory vs dicontinuation) during PMR process and follow up action plan to reduce inventory balance to reduce 50% gap in next 12 months 
+3. Identify every monyth oversales/undersales due to BO to isolate KPI to real world refocusing action plant in commercial/suplly
+4. Identify every month reserve vs commercial action plan to avoid WO and maximize to less than 1% 
+5. Negotiate with AGI 100% PO with delays and take revenue recognition to avoid WO impact in our cluster
+6. Develope Argentina 3PL business  in H1 for direct sales and negotiate with disprofarma after that to move down in 1 ppt total distribution cost at least
+7. Manage Cenabast tender distribution in Chile in amonthly base tacking care not surpass 3% of overall cost in budget
+8. Review clients with more than 4 deliveries by month to reduce it during H1, impacting H2 in both countries
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. X Brand FA 
+2. % gap reduction
+3. ppt deviation
+4. less than 1%
+5. 1
+6. cut 1ppt 
+7. &lt; 3%
+8. # orders
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Support Organic and Inorganic Growth</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Monitor monthly in advance during IBP process promoted product accuracy to tackle budget numbers and avoid more than 3% deviation over that
+2. Deeper understanding of market audits (potential or real impacts) into 80/20 promoted brands monthly/quartely to avoid more than 3% deviation over budget units
+3. Develop price list in a monythly base tacking into account inflation, market dynamics and PAMI/Union HMOs discounts to align net prices to budget prices and deviation no more than 3%
+4. Define for end of July 25 NBD projects and timeline impact for South Cone
+5. Present to RC during Q1 potential business opportunities to scalate to SA could impact into FY 2026
+6. Monitor current last year NBD products in Argentina performance vs budget in a monthly base achieving overperformance of 5% at least
+7. Obtain Elidel MAT in Uruguay during Q3 FY 26 and start business in Q4
+8. Obtain Clozapina MAT in Q4 2026 to start business in FY 2027
+9. Maintain 100% of current MAT in Chile/Argentina and Uruguay with cero deviation or cancelations
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Budget units
+2. % deviation
+3. % deviation
+4. PPT
+5. PPT
+6. &gt; 5%
+7. MAT
+8. MAt
+9. % MAT 
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Reinforce internal procedures and controls</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Obtain in next 6 audits to run in Argentina during FY 2026  good or satisfactory
+2. To be open to external audit and answer into due dates according future requerimentsduring FY 2026
+3. Perform during FY 2026 according due dates action plan for Sales audit run during FY 2025 to acieve 100% of pints closed 
+4. 100% completion of all governance documents required by Group during FY 2026 into due dates 
+5. Set 100% review/approve working papers following external audit guidance to address internal/external audits during FY2026
+6. Drive QBSR (Quaterly Balance Sheet review) in a quaterly base during FY 2026
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Ratio
+2. TBD
+3. Due dates
+4. 1
+5. 1
+6. 4  in total
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Enhance Talent </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Run nine box at second level during Q2 2026 
+2. Develope PID to implement during H2 2026 for those succesors 
+3. Follow up/update salaries/benefit in Argentina aligned to inflation and market values every Quarter during FY 2026
+4. Ensure that 100% of employees are registered on the platform 30 days after platform availability in spanish.
+5. Train southern cone' employees in Tess Learning System after employees registered in the next 30 days
+6. Run 100% of courses in TESS during FY 2026 according establish due dates 
+7. To reinforce process and timeline during Q1 to 100% employess with teams on charge 
+8. Communicate monthly base all Aspen vacancies into the referral policy
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. 100% in Q2
+2. 100% in H2
+3. 
+4. 1
+5. 1
+6. 1
+7. Q1
+8. FY
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">María Belén López  </x:t>
+  </x:si>
+  <x:si>
+    <x:t>Coordinadora de Crédito y Cobranzas</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">"1. Set ""recurring expenses"" report to ensure montlhy booking and payment ensuring services are ""always"" on line and avoid interest charges.
+2. Set monthly ""Accounts Receivable"" tracker to ensure collections on time and avoid need of Bad Debt reserve.
+3. Set Cash quaterly flow plan and comparison to actual execution to find process improvements."
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">"1. Monthly Recurring report.
+2. Collection report.
+3. Cash flow report.
+"
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">"1. Track monthly overdue invoices and following up until collection/credit note
+2. Research and investigate discrepancies in invoices (prices/discounts) and follow up until mgmnt approval/rejection
+3. Execute 60 days in ARG and 30 days in CHI pay term plan
+4. Place extra cash at overnight low risk interest"
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">"1. Collection report
+2. Collection report
+3. DSO report, DPO report
+4. Monthly interest report"
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">"1. Completion of all governance documents required by Group
+2. Set ""review/approve"" working papers following external audit guidance to address internal/external audits more effectively."
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">"1. TESS report
+2. Audit reports."
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Follow up TESS execution quaterly.
+Update/review job desciptions to ensure faster staffing (in case necessary) by Dec-2026"
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">"1. Goals filing special section
+2. TESS report
+3. Updated job description"
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Jazzmín Eden Gutierrez Rodríguez </x:t>
+  </x:si>
+  <x:si>
+    <x:t>Jefe de Planeación Financiera Cono Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">"1. Deliver monthly and accurate reports to file P&amp;L 
+2. Set controls to analyze opex and facilitate decision making (actual vs plan/forecast) on events
+3. Prepare detailed plan / forecast to ensure future best execution and follow-up.
+4. Guide actuals teams to ensure  plan/fcst rationale are booked as planned."
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">"1. Montlhy Report
+2. SOLPED process
+3. F2 and Plan filing
+4. Month end close check-list"
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">"1. Deliver monthly and accurate reports to file Working Capital.
+2. Guide actuals teams to ensure  plan/fcst rationale are booked as planned."
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Monthly report
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Perform analysis to support commercial and marketing actions/improvements to foster sales/performance)
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Weekly sales tracker
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">"1. Completion of all governance documents required by Group
+2. Set ""review/approve"" working papers following external audit guidance to address internal/external audits more effectively.
+3. Drive QBSR (Quaterly Balance Sheet review) quaterly."
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">"1. TESS report
+2. Audit reports
+3. QBSR report"
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">"Complete short and long term of ""me, my view"" semesterly.
+Follow up TESS execution quaterly.
+Update/review job desciptions to ensure faster staffing (in case necessary) by Dec-2026"
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Brahiam Bachir Massoud </x:t>
+  </x:si>
+  <x:si>
+    <x:t>Coordinador de Compras</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Procurement Plan/Strategy &amp; Savings</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. Set procurement plan/strategy aiming to identify where open orders, contracts or other actios prevent from issuing every single Purchase orders before Dec-2026
+2. Perform procurement efficiently aiming 5% ensuring quality and Aspen's standards.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Action plan
+2. Savings control sheets </x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. Reinforce SOLPED process implementation by updating and (re)training and also communicating new actios for Purchase Orders such as contacts, open orders and direct purchases.
+2. Coorinate "Contracts" regional tool to ensure regional compliance on events.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. Montly reminder, Quaterly re-training
+2. Contract tool</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. Complete short and long term of "me, my view" semesterly.
+2. Follow up TESS execution quaterly.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. Goals filing special section
+2. TESS report</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Boris Arteaga González</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Coordinador Contable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Alcanzar el EBITDA presupuestado para el año fiscal 2026 (22,4 millones de euros)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. Garantizar la correcta imputación de los hechos financieros en los libros contables                                                                  
+2. Análisis y Control de la PPV                                                                                                                               
+3. Buscar puntos de mejora que permitan mayor eficiencia en los procesos. (sobre todo los que vienen de terceros)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Chequear los cierres mensuales mediante check list                            
+2. F2 y Presupuesto                   </x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mejorar el capital de trabajo</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Armado mensual de papeles de trabajo para mostrar la pertinencia de las cuentas del balance (cuentas por pagar, cuentas por cobrar) </x:t>
+  </x:si>
+  <x:si>
+    <x:t>Reporte Mensual</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Reforzar procedimientos y controles internos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. Armado de trial balance trimestral con los anexos para la revision de cada rubro                                                                2.Preparar Soportes claros y oportunos para las Auditorias  3.Papel de trabajo mensual donde se concilien todas las cuentas relacionadas con las ventas  (impositivas y de resultados)                                                                                                        3. Revision de la informacion sumistrada por los estudios impositivos y demas, de manera mensual ademas desarrolar Calendario tributario</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. QBRS report                                       2. Audit Report  </x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mejorar el talento</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Elaboración de entrenamientos enviados por la compañía en tiempo y forma                                                                                                                                      2. Elaboración de descripción del puesto de trabajo para diciembre 2025                                                                                                                                                                    3. Revisión activa de los objetivos cada 6 meses                                                                            </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Revision de Objetivos
+2. TESS report
+3. Descripcion de puesto de trabajo actualizada </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Objetivo - Área Clave de Desempeño (KPA)	</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Deliver timely and accurate reports to file IRR
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. IRR monthly report
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Luca Nahuel Ruiz </x:t>
+  </x:si>
+  <x:si>
+    <x:t>Analista Contable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. Garantizar la correcta imputacion de los hechos financieros en los libros contables.
+2. Analisis y Control de la PPV.
+3. Buscar puntos de mejora que permitan mayor eficiencia en los procesos. (sobre todo los que vienen de terceros)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Chequear los cierres mensuales mediante check list.
+2. F2 y Presupuesto     </x:t>
+  </x:si>
+  <x:si>
+    <x:t>Para mejorar el capital de trabajo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. Armado mensual de papeles de trabajo para mostrar la pertinencia de las cuentas del balance (cuentas por pagar, cuentas por cobrar).</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. Monthly report</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Reforzar los procedimientos y controles internos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. Armado de trial balance trimestral con los anexos para la revision de cada rubro.
+2. Preparar Soportes claros y oportunos para las Auditorias  
+3. Papel de trabajo mensual donde se concilien todas las cuentas relacionadas con las ventas  (impositivas y de resultados).
+4. Revision de la informacion sumistrada por los estudios impositivos y demas, de manera mensual ademas desarrolar Calendario tributario.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. QBRS report
+2. Audit Report </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Elaboración de entrenamientos enviados por la compañía en tiempo y forma.
+2. Elaboración de descripción del puesto de trabajo para diciembre 2025.
+3. Revision activa de los objetivos cada 6 meses            </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Revisión de Objetivos
+2. TESS report
+3. Descripción de puesto de trabajo actualizada </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Rodrigo Alexander Baez </x:t>
+  </x:si>
+  <x:si>
+    <x:t>Analista de Planeación Financiera</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Revisar la geneneracion de las Solped para procurar por la correcta imputacion de los gastos  (Ceco /cuenta/asignacion del preupuesto) y dar el soporte necesario a las diferentes areas en tanto lo requieran.                                                                                                      2.Preparar el Monthly y los detalles que lo soporten                                                                                    3. Preparar los detalles para el armado y control  de F2 y Pesupuesto.                                                                                                    4.  Mantenimiento mensual y desarrollo de herramientas que permitan el analisis agil de la informacion presupuestaria (PBI , otros)                                                                                                                   5. Realizar validacion de las ventas y el costo del reporte mensual con el sistema TM1 y evitar diferencias con planning regional </x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. Proceso de solped                                    2. Montlhy Report                                                 3. Chequear los cierres mesnsuales mediante check list                                  4.F2 y Presupuesto</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1.Elaboracion de repores  intermedios  que permitan a la gerencia un analisi previo de los resultados  ()                                                                                                                                                 2.Interaccion activa con el equipo contable para buscar  mejoras  en los procesos                                                                                                                                                                                        </x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lograr la precisión del plan de demanda</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Elaboracion /analisis/ Automatizacion del IRR (1)
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Apoyar el crecimiento orgánico e inorgánico</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Control de precio con los descuentos que correspa     (reporte comparativa Precios)                                                                             2. Analizar el margen de rentabilidad  por  SKU para establecer el peso de cada uno dentro del total y compartirlo al area comercial y de marketing                                                      
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1.Proporcionar soportes claros que sirvan para las auditorias  (para mirar Mitad de año)                                                                                                                                                                    2.Participar de la implementacion de la  nueva herramienta de entrenamientos 
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">"1. TESS report
+2. Audit reports
+3. QBSR reporte"
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Elaboracion de entrenamientos enviados por la compañía en tiempo y forma                                                                                                                                                         2. Elaboracion de descripcion del puesto de trabajo para diciembre 2025                                                                                             3. Revision activa de los objetivos cada 6 meses                                                                           
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">"1. Revisdion de Objetivos
+2. TESS report
+3. Descripcion de puesto de trabajo actualizada "
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Paola Alejandra Napolitano </x:t>
+  </x:si>
+  <x:si>
+    <x:t>Analista de Tesorería</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">"1. Set ""recurring expenses"" report to ensure montlhy booking and payment ensuring services are ""always"" on line and avoid interest charges.
+2. Set Cash quaterly flow plan and comparison to actual execution to find process improvements."
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">"1. Monthly Recurring report.
+2. Cash flow report.
+"
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">"1. Track monthly overdue invoices and following up 
+2. Research and investigate discrepancies in invoices and following up
+3. Execute 60 days in ARG and 30 days in CHI pay term plan
+4. Place extra cash at overnight low risk interest"
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">"1. Collection report
+2. Collection report
+3.  DPO report
+4. Monthly interest report"
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Matías Nicolás Perillo </x:t>
+  </x:si>
+  <x:si>
+    <x:t>Analista de Crédito y Cobranzas</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">3. Set Cash quaterly flow plan and comparison to actual execution to find process improvements.
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">2. Collection report.
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Track monthly overdue invoices and following up until collection/credit note
+2. Research and investigate discrepancies in invoices (prices/discounts) and follow up until mgmnt approval/rejection
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. Collection report
+2. Collection report</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Completion of all governance documents required by Group
+2. Set ""review/approve"" working papers following external audit guidance to address internal/external audits more effectively."
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. TESS report
+2. Audit reports.
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Complete short and long term of ""me, my view"" semesterly.
+Follow up TESS execution quaterly.
+Update/review job desciptions to ensure faster staffing (in case necessary) by Dec-2026
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Goals filing special section
+2. TESS report
+3. Updated job description
+</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -106,31 +630,52 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="4">
+  <x:cellStyleXfs count="7">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="4">
+  <x:cellXfs count="7">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
@@ -432,15 +977,13 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K1"/>
+  <x:dimension ref="A1:K42"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="15.710625" style="0" customWidth="1"/>
     <x:col min="2" max="4" width="35.710625" style="0" customWidth="1"/>
-    <x:col min="5" max="6" width="40.710625" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="40.710625" style="3" customWidth="1"/>
-    <x:col min="8" max="8" width="45.710625" style="3" customWidth="1"/>
-    <x:col min="9" max="11" width="45.710625" style="0" customWidth="1"/>
+    <x:col min="5" max="7" width="40.710625" style="0" customWidth="1"/>
+    <x:col min="8" max="11" width="45.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:11" s="1" customFormat="1">
@@ -462,10 +1005,10 @@
       <x:c r="F1" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G1" s="2" t="s">
+      <x:c r="G1" s="1" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H1" s="2" t="s">
+      <x:c r="H1" s="1" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="I1" s="1" t="s">
@@ -475,6 +1018,1277 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="K1" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:11" s="2" customFormat="1">
+      <x:c r="A2" s="2" t="n">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B2" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C2" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E2" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F2" s="2" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G2" s="3" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H2" s="3" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I2" s="2" t="s"/>
+      <x:c r="J2" s="2" t="s"/>
+      <x:c r="K2" s="2" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:11" s="4" customFormat="1">
+      <x:c r="A3" s="4" t="n">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B3" s="4" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C3" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D3" s="4" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E3" s="4" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F3" s="4" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G3" s="5" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H3" s="5" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I3" s="4" t="s"/>
+      <x:c r="J3" s="4" t="s"/>
+      <x:c r="K3" s="4" t="n">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:11" s="2" customFormat="1">
+      <x:c r="A4" s="2" t="n">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B4" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C4" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D4" s="2" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E4" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F4" s="2" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G4" s="3" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H4" s="3" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="I4" s="2" t="s"/>
+      <x:c r="J4" s="2" t="s"/>
+      <x:c r="K4" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:11" s="4" customFormat="1">
+      <x:c r="A5" s="4" t="n">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B5" s="4" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C5" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D5" s="4" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E5" s="4" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F5" s="4" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G5" s="5" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H5" s="5" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I5" s="4" t="s"/>
+      <x:c r="J5" s="4" t="s"/>
+      <x:c r="K5" s="4" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:11" s="2" customFormat="1">
+      <x:c r="A6" s="2" t="n">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B6" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C6" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D6" s="2" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E6" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F6" s="2" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G6" s="3" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H6" s="3" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="I6" s="2" t="s"/>
+      <x:c r="J6" s="2" t="s"/>
+      <x:c r="K6" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:11" s="4" customFormat="1">
+      <x:c r="A7" s="4" t="n">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B7" s="4" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C7" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D7" s="4" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E7" s="4" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F7" s="4" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G7" s="5" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H7" s="5" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I7" s="4" t="s"/>
+      <x:c r="J7" s="4" t="s"/>
+      <x:c r="K7" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:11" s="2" customFormat="1">
+      <x:c r="A8" s="2" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B8" s="2" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C8" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D8" s="2" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E8" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F8" s="2" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G8" s="3" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H8" s="3" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="I8" s="2" t="s"/>
+      <x:c r="J8" s="2" t="s"/>
+      <x:c r="K8" s="2" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:11" s="4" customFormat="1">
+      <x:c r="A9" s="4" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B9" s="4" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C9" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D9" s="4" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E9" s="4" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F9" s="4" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G9" s="5" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H9" s="5" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="I9" s="4" t="s"/>
+      <x:c r="J9" s="4" t="s"/>
+      <x:c r="K9" s="4" t="n">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:11" s="2" customFormat="1">
+      <x:c r="A10" s="2" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B10" s="2" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C10" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D10" s="2" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E10" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F10" s="2" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G10" s="3" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H10" s="3" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I10" s="2" t="s"/>
+      <x:c r="J10" s="2" t="s"/>
+      <x:c r="K10" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:11" s="4" customFormat="1">
+      <x:c r="A11" s="4" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B11" s="4" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C11" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D11" s="4" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E11" s="4" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F11" s="4" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G11" s="5" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H11" s="5" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="I11" s="4" t="s"/>
+      <x:c r="J11" s="4" t="s"/>
+      <x:c r="K11" s="4" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:11" s="2" customFormat="1">
+      <x:c r="A12" s="2" t="n">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B12" s="2" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C12" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D12" s="2" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E12" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F12" s="2" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G12" s="3" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H12" s="3" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="I12" s="2" t="s"/>
+      <x:c r="J12" s="2" t="s"/>
+      <x:c r="K12" s="2" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:11" s="4" customFormat="1">
+      <x:c r="A13" s="4" t="n">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B13" s="4" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C13" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D13" s="4" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E13" s="4" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F13" s="4" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G13" s="5" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H13" s="5" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="I13" s="4" t="s"/>
+      <x:c r="J13" s="4" t="s"/>
+      <x:c r="K13" s="4" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:11" s="2" customFormat="1">
+      <x:c r="A14" s="2" t="n">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B14" s="2" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C14" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D14" s="2" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E14" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F14" s="2" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G14" s="3" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H14" s="3" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="I14" s="2" t="s"/>
+      <x:c r="J14" s="2" t="s"/>
+      <x:c r="K14" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:11" s="4" customFormat="1">
+      <x:c r="A15" s="4" t="n">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B15" s="4" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C15" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D15" s="4" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E15" s="4" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F15" s="4" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G15" s="5" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H15" s="5" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="I15" s="4" t="s"/>
+      <x:c r="J15" s="4" t="s"/>
+      <x:c r="K15" s="4" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:11" s="2" customFormat="1">
+      <x:c r="A16" s="2" t="n">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B16" s="2" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C16" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D16" s="2" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E16" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F16" s="2" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G16" s="3" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H16" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="I16" s="2" t="s"/>
+      <x:c r="J16" s="2" t="s"/>
+      <x:c r="K16" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:11" s="4" customFormat="1">
+      <x:c r="A17" s="4" t="n">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B17" s="4" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C17" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D17" s="4" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E17" s="4" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F17" s="4" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G17" s="5" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H17" s="5" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="I17" s="4" t="s"/>
+      <x:c r="J17" s="4" t="s"/>
+      <x:c r="K17" s="4" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:11" s="2" customFormat="1">
+      <x:c r="A18" s="2" t="n">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B18" s="2" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C18" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D18" s="2" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E18" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F18" s="2" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G18" s="3" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="H18" s="3" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I18" s="2" t="s"/>
+      <x:c r="J18" s="2" t="s"/>
+      <x:c r="K18" s="2" t="n">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:11" s="4" customFormat="1">
+      <x:c r="A19" s="4" t="n">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B19" s="4" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C19" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D19" s="4" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E19" s="4" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F19" s="4" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G19" s="5" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H19" s="5" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="I19" s="4" t="s"/>
+      <x:c r="J19" s="4" t="s"/>
+      <x:c r="K19" s="4" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:11" s="2" customFormat="1">
+      <x:c r="A20" s="2" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B20" s="2" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C20" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D20" s="2" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E20" s="2" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F20" s="2" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G20" s="3" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H20" s="3" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I20" s="2" t="s"/>
+      <x:c r="J20" s="2" t="s"/>
+      <x:c r="K20" s="2" t="n">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:11" s="4" customFormat="1">
+      <x:c r="A21" s="4" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B21" s="4" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C21" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D21" s="4" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E21" s="4" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F21" s="4" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G21" s="4" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H21" s="4" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="I21" s="4" t="s"/>
+      <x:c r="J21" s="4" t="s"/>
+      <x:c r="K21" s="4" t="n">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:11" s="2" customFormat="1">
+      <x:c r="A22" s="2" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B22" s="2" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C22" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D22" s="2" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E22" s="2" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F22" s="2" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G22" s="2" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="H22" s="2" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="I22" s="2" t="s"/>
+      <x:c r="J22" s="2" t="s"/>
+      <x:c r="K22" s="2" t="n">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:11" s="4" customFormat="1">
+      <x:c r="A23" s="4" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B23" s="4" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C23" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D23" s="4" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E23" s="4" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F23" s="4" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G23" s="4" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="H23" s="5" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="I23" s="4" t="s"/>
+      <x:c r="J23" s="4" t="s"/>
+      <x:c r="K23" s="4" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:11" s="2" customFormat="1">
+      <x:c r="A24" s="2" t="n">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B24" s="2" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C24" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D24" s="2" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E24" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F24" s="2" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G24" s="3" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H24" s="3" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="I24" s="2" t="s"/>
+      <x:c r="J24" s="2" t="s"/>
+      <x:c r="K24" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:11" s="4" customFormat="1">
+      <x:c r="A25" s="4" t="n">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B25" s="4" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C25" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D25" s="4" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E25" s="4" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F25" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G25" s="5" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="H25" s="5" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="I25" s="4" t="s"/>
+      <x:c r="J25" s="4" t="s"/>
+      <x:c r="K25" s="4" t="n">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:11" s="2" customFormat="1">
+      <x:c r="A26" s="2" t="n">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B26" s="2" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C26" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D26" s="2" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E26" s="2" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F26" s="2" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G26" s="2" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="H26" s="2" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="I26" s="2" t="s"/>
+      <x:c r="J26" s="2" t="s"/>
+      <x:c r="K26" s="2" t="n">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:11" s="4" customFormat="1">
+      <x:c r="A27" s="4" t="n">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B27" s="4" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C27" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D27" s="4" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E27" s="4" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F27" s="4" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G27" s="5" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="H27" s="5" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="I27" s="4" t="s"/>
+      <x:c r="J27" s="4" t="s"/>
+      <x:c r="K27" s="4" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:11" s="2" customFormat="1">
+      <x:c r="A28" s="2" t="n">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B28" s="2" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C28" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D28" s="2" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E28" s="2" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F28" s="2" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G28" s="3" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="H28" s="3" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="I28" s="2" t="s"/>
+      <x:c r="J28" s="2" t="s"/>
+      <x:c r="K28" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:11" s="4" customFormat="1">
+      <x:c r="A29" s="4" t="n">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="B29" s="4" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C29" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D29" s="4" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="E29" s="4" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F29" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G29" s="4" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="H29" s="4" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="I29" s="4" t="s"/>
+      <x:c r="J29" s="4" t="s"/>
+      <x:c r="K29" s="4" t="n">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:11" s="2" customFormat="1">
+      <x:c r="A30" s="2" t="n">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="B30" s="2" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C30" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D30" s="2" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="E30" s="2" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F30" s="2" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G30" s="2" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="H30" s="3" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="I30" s="2" t="s"/>
+      <x:c r="J30" s="2" t="s"/>
+      <x:c r="K30" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:11" s="4" customFormat="1">
+      <x:c r="A31" s="4" t="n">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="B31" s="4" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C31" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D31" s="4" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="E31" s="4" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F31" s="4" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="G31" s="5" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H31" s="5" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="I31" s="4" t="s"/>
+      <x:c r="J31" s="4" t="s"/>
+      <x:c r="K31" s="4" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:11" s="2" customFormat="1">
+      <x:c r="A32" s="2" t="n">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="B32" s="2" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C32" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D32" s="2" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="E32" s="2" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F32" s="2" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="G32" s="3" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="H32" s="3" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="I32" s="2" t="s"/>
+      <x:c r="J32" s="2" t="s"/>
+      <x:c r="K32" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:11" s="4" customFormat="1">
+      <x:c r="A33" s="4" t="n">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="B33" s="4" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C33" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D33" s="4" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="E33" s="4" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F33" s="4" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G33" s="5" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H33" s="5" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="I33" s="4" t="s"/>
+      <x:c r="J33" s="4" t="s"/>
+      <x:c r="K33" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:11" s="2" customFormat="1">
+      <x:c r="A34" s="2" t="n">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="B34" s="2" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C34" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D34" s="2" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="E34" s="2" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F34" s="2" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G34" s="3" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="H34" s="3" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="I34" s="2" t="s"/>
+      <x:c r="J34" s="2" t="s"/>
+      <x:c r="K34" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:11" s="4" customFormat="1">
+      <x:c r="A35" s="4" t="n">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="B35" s="4" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C35" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D35" s="4" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="E35" s="4" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F35" s="4" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G35" s="5" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="H35" s="5" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="I35" s="4" t="s"/>
+      <x:c r="J35" s="4" t="s"/>
+      <x:c r="K35" s="4" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:11" s="2" customFormat="1">
+      <x:c r="A36" s="2" t="n">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="B36" s="2" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C36" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D36" s="2" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="E36" s="2" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F36" s="2" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G36" s="3" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="H36" s="3" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="I36" s="2" t="s"/>
+      <x:c r="J36" s="2" t="s"/>
+      <x:c r="K36" s="2" t="n">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:11" s="4" customFormat="1">
+      <x:c r="A37" s="4" t="n">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="B37" s="4" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C37" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D37" s="4" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="E37" s="4" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F37" s="4" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G37" s="5" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H37" s="5" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I37" s="4" t="s"/>
+      <x:c r="J37" s="4" t="s"/>
+      <x:c r="K37" s="4" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:11" s="2" customFormat="1">
+      <x:c r="A38" s="2" t="n">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="B38" s="2" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C38" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D38" s="2" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="E38" s="2" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F38" s="2" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G38" s="3" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H38" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="I38" s="2" t="s"/>
+      <x:c r="J38" s="2" t="s"/>
+      <x:c r="K38" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:11" s="4" customFormat="1">
+      <x:c r="A39" s="4" t="n">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="B39" s="4" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C39" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D39" s="4" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="E39" s="4" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F39" s="4" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G39" s="5" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="H39" s="5" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="I39" s="4" t="s"/>
+      <x:c r="J39" s="4" t="s"/>
+      <x:c r="K39" s="4" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:11" s="2" customFormat="1">
+      <x:c r="A40" s="2" t="n">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="B40" s="2" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C40" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D40" s="2" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="E40" s="2" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F40" s="2" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G40" s="3" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="H40" s="3" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="I40" s="2" t="s"/>
+      <x:c r="J40" s="2" t="s"/>
+      <x:c r="K40" s="2" t="n">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:11" s="4" customFormat="1">
+      <x:c r="A41" s="4" t="n">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="B41" s="4" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C41" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D41" s="4" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="E41" s="4" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F41" s="4" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G41" s="5" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="H41" s="5" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="I41" s="4" t="s"/>
+      <x:c r="J41" s="4" t="s"/>
+      <x:c r="K41" s="4" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:11">
+      <x:c r="A42" s="0" t="n">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D42" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="E42" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F42" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G42" s="6" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="H42" s="6" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="I42" s="0" t="s"/>
+      <x:c r="J42" s="0" t="s"/>
+      <x:c r="K42" s="0" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
